--- a/data/stock_harian.xlsx
+++ b/data/stock_harian.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fifo365-my.sharepoint.com/personal/68766_fif_co_id/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="217" documentId="8_{8EAF207E-0644-4A14-8133-8B1A9C3F05A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94B0E4E6-0213-40E4-8D40-FC8050172EC2}"/>
+  <xr:revisionPtr revIDLastSave="227" documentId="8_{8EAF207E-0644-4A14-8133-8B1A9C3F05A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{422D7998-A608-4893-98BC-7761C9E9CAF2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{503EE100-7F29-40DA-810E-518CED29D0C3}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">stock_harian!$A$1:$N$385</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">stock_harian!$A$1:$N$448</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -6678,6 +6678,10 @@
 </externalLink>
 </file>
 
+<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
+<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -19802,7 +19806,7 @@
         <v>46153</v>
       </c>
       <c r="B268" s="10" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C268" s="13">
         <v>3</v>
@@ -20810,7 +20814,7 @@
         <v>46153</v>
       </c>
       <c r="B289" s="10" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C289" s="13">
         <v>8</v>
@@ -21818,7 +21822,7 @@
         <v>46153</v>
       </c>
       <c r="B310" s="10" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C310" s="13">
         <v>9</v>
@@ -22850,7 +22854,7 @@
         <v>46154</v>
       </c>
       <c r="B331" s="10" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C331" s="13">
         <v>3</v>
@@ -23921,7 +23925,7 @@
         <v>46154</v>
       </c>
       <c r="B352" s="10" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C352" s="13">
         <v>8</v>
@@ -24992,7 +24996,7 @@
         <v>46154</v>
       </c>
       <c r="B373" s="10" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C373" s="13">
         <v>9</v>
@@ -26007,7 +26011,7 @@
         <v>46155</v>
       </c>
       <c r="B394" s="10" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C394" s="13">
         <v>3</v>
@@ -26931,7 +26935,7 @@
         <v>46155</v>
       </c>
       <c r="B415" s="10" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C415" s="13">
         <v>8</v>
@@ -27855,7 +27859,7 @@
         <v>46155</v>
       </c>
       <c r="B436" s="10" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C436" s="13">
         <v>9</v>
@@ -28423,7 +28427,7 @@
       <c r="N448" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N385" xr:uid="{B95951AB-A916-4397-AA75-837BDA15EBEB}"/>
+  <autoFilter ref="A1:N448" xr:uid="{B95951AB-A916-4397-AA75-837BDA15EBEB}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/stock_harian.xlsx
+++ b/data/stock_harian.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fifo365-my.sharepoint.com/personal/68766_fif_co_id/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="323" documentId="8_{8EAF207E-0644-4A14-8133-8B1A9C3F05A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E7B2102-9721-44DA-A698-61E5F1435E3B}"/>
+  <xr:revisionPtr revIDLastSave="330" documentId="8_{8EAF207E-0644-4A14-8133-8B1A9C3F05A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{150E5AF3-CECE-4FEF-8125-8F97525AAA8A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{503EE100-7F29-40DA-810E-518CED29D0C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{503EE100-7F29-40DA-810E-518CED29D0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="stock_harian" sheetId="1" r:id="rId1"/>
@@ -6877,6 +6877,10 @@
 </externalLink>
 </file>
 
+<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
+<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Andi Farras Thariq Hasibuan" id="{7AD5508D-0AF0-4DEE-9664-71FEE2B78628}" userId="S::68766@fif.co.id::cc0bbbe6-0d0b-4bec-8e41-e17e17e68d4e" providerId="AD"/>
@@ -23671,7 +23675,7 @@
         <v>0</v>
       </c>
       <c r="N323" s="12">
-        <f t="shared" ref="N323:N385" si="16">MAX($I323-$M323,0)</f>
+        <f t="shared" ref="N323:N386" si="16">MAX($I323-$M323,0)</f>
         <v>4</v>
       </c>
       <c r="O323" s="14">
@@ -27071,12 +27075,12 @@
       <c r="M386" s="56">
         <v>0</v>
       </c>
-      <c r="N386" s="62">
-        <f t="shared" ref="N386:N417" si="21">MAX($I386-$M386,0)</f>
+      <c r="N386" s="12">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O386" s="65">
-        <f t="shared" ref="O386:O417" si="22">N386*D386</f>
+        <f t="shared" ref="O386:O417" si="21">N386*D386</f>
         <v>0</v>
       </c>
     </row>
@@ -27118,19 +27122,19 @@
       </c>
       <c r="K387" s="60"/>
       <c r="L387" s="13">
-        <f t="shared" ref="L387:L418" si="23">IF(H387&gt;MAX(G387-M387,0),MAX(G387-M387,0),H387)</f>
+        <f t="shared" ref="L387:L418" si="22">IF(H387&gt;MAX(G387-M387,0),MAX(G387-M387,0),H387)</f>
         <v>0</v>
       </c>
       <c r="M387" s="56">
-        <v>0</v>
-      </c>
-      <c r="N387" s="62">
+        <v>6</v>
+      </c>
+      <c r="N387" s="12">
+        <f t="shared" ref="N387:N448" si="23">MAX($I387-$M387,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O387" s="65">
         <f t="shared" si="21"/>
-        <v>6</v>
-      </c>
-      <c r="O387" s="65">
-        <f t="shared" si="22"/>
-        <v>138000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -27171,19 +27175,19 @@
       </c>
       <c r="K388" s="60"/>
       <c r="L388" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M388" s="56">
+        <v>1</v>
+      </c>
+      <c r="N388" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M388" s="56">
-        <v>0</v>
-      </c>
-      <c r="N388" s="62">
+      <c r="O388" s="65">
         <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="O388" s="65">
-        <f t="shared" si="22"/>
-        <v>21000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="389" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -27224,19 +27228,19 @@
       </c>
       <c r="K389" s="60"/>
       <c r="L389" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M389" s="56">
+        <v>2</v>
+      </c>
+      <c r="N389" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M389" s="56">
-        <v>0</v>
-      </c>
-      <c r="N389" s="62">
+      <c r="O389" s="65">
         <f t="shared" si="21"/>
-        <v>2</v>
-      </c>
-      <c r="O389" s="65">
-        <f t="shared" si="22"/>
-        <v>72000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="390" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -27277,18 +27281,18 @@
       </c>
       <c r="K390" s="60"/>
       <c r="L390" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M390" s="56">
+        <v>0</v>
+      </c>
+      <c r="N390" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M390" s="56">
-        <v>0</v>
-      </c>
-      <c r="N390" s="62">
+      <c r="O390" s="65">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="O390" s="65">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -27330,19 +27334,19 @@
       </c>
       <c r="K391" s="60"/>
       <c r="L391" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M391" s="56">
+        <v>6</v>
+      </c>
+      <c r="N391" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M391" s="56">
-        <v>0</v>
-      </c>
-      <c r="N391" s="62">
+      <c r="O391" s="65">
         <f t="shared" si="21"/>
-        <v>6</v>
-      </c>
-      <c r="O391" s="65">
-        <f t="shared" si="22"/>
-        <v>90000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -27383,19 +27387,19 @@
       </c>
       <c r="K392" s="60"/>
       <c r="L392" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M392" s="56">
+        <v>2</v>
+      </c>
+      <c r="N392" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M392" s="56">
-        <v>0</v>
-      </c>
-      <c r="N392" s="62">
+      <c r="O392" s="65">
         <f t="shared" si="21"/>
-        <v>2</v>
-      </c>
-      <c r="O392" s="65">
-        <f t="shared" si="22"/>
-        <v>36000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="393" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -27436,18 +27440,18 @@
       </c>
       <c r="K393" s="60"/>
       <c r="L393" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M393" s="56">
+        <v>0</v>
+      </c>
+      <c r="N393" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M393" s="56">
-        <v>0</v>
-      </c>
-      <c r="N393" s="62">
+      <c r="O393" s="65">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="O393" s="65">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -27489,19 +27493,19 @@
       </c>
       <c r="K394" s="60"/>
       <c r="L394" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M394" s="56">
+        <v>2</v>
+      </c>
+      <c r="N394" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M394" s="56">
-        <v>0</v>
-      </c>
-      <c r="N394" s="62">
+      <c r="O394" s="65">
         <f t="shared" si="21"/>
-        <v>2</v>
-      </c>
-      <c r="O394" s="65">
-        <f t="shared" si="22"/>
-        <v>70000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -27542,19 +27546,19 @@
       </c>
       <c r="K395" s="60"/>
       <c r="L395" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M395" s="56">
+        <v>4</v>
+      </c>
+      <c r="N395" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M395" s="56">
-        <v>0</v>
-      </c>
-      <c r="N395" s="62">
+      <c r="O395" s="65">
         <f t="shared" si="21"/>
-        <v>4</v>
-      </c>
-      <c r="O395" s="65">
-        <f t="shared" si="22"/>
-        <v>160000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="396" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -27595,19 +27599,19 @@
       </c>
       <c r="K396" s="60"/>
       <c r="L396" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M396" s="56">
+        <v>3</v>
+      </c>
+      <c r="N396" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M396" s="56">
-        <v>0</v>
-      </c>
-      <c r="N396" s="62">
+      <c r="O396" s="65">
         <f t="shared" si="21"/>
-        <v>3</v>
-      </c>
-      <c r="O396" s="65">
-        <f t="shared" si="22"/>
-        <v>7500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="397" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -27648,19 +27652,19 @@
       </c>
       <c r="K397" s="60"/>
       <c r="L397" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M397" s="56">
+        <v>10</v>
+      </c>
+      <c r="N397" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M397" s="56">
-        <v>0</v>
-      </c>
-      <c r="N397" s="62">
+      <c r="O397" s="65">
         <f t="shared" si="21"/>
-        <v>10</v>
-      </c>
-      <c r="O397" s="65">
-        <f t="shared" si="22"/>
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -27701,19 +27705,19 @@
       </c>
       <c r="K398" s="60"/>
       <c r="L398" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M398" s="56">
+        <v>10</v>
+      </c>
+      <c r="N398" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M398" s="56">
-        <v>0</v>
-      </c>
-      <c r="N398" s="62">
+      <c r="O398" s="65">
         <f t="shared" si="21"/>
-        <v>10</v>
-      </c>
-      <c r="O398" s="65">
-        <f t="shared" si="22"/>
-        <v>25000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="399" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -27754,19 +27758,19 @@
       </c>
       <c r="K399" s="60"/>
       <c r="L399" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M399" s="56">
+        <v>15</v>
+      </c>
+      <c r="N399" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M399" s="56">
-        <v>0</v>
-      </c>
-      <c r="N399" s="62">
+      <c r="O399" s="65">
         <f t="shared" si="21"/>
-        <v>15</v>
-      </c>
-      <c r="O399" s="65">
-        <f t="shared" si="22"/>
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="400" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -27807,19 +27811,19 @@
       </c>
       <c r="K400" s="60"/>
       <c r="L400" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M400" s="56">
+        <v>10</v>
+      </c>
+      <c r="N400" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M400" s="56">
-        <v>0</v>
-      </c>
-      <c r="N400" s="62">
+      <c r="O400" s="65">
         <f t="shared" si="21"/>
-        <v>10</v>
-      </c>
-      <c r="O400" s="65">
-        <f t="shared" si="22"/>
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="401" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -27860,19 +27864,19 @@
       </c>
       <c r="K401" s="60"/>
       <c r="L401" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M401" s="56">
+        <v>5</v>
+      </c>
+      <c r="N401" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M401" s="56">
-        <v>0</v>
-      </c>
-      <c r="N401" s="62">
+      <c r="O401" s="65">
         <f t="shared" si="21"/>
-        <v>5</v>
-      </c>
-      <c r="O401" s="65">
-        <f t="shared" si="22"/>
-        <v>115000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="402" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -27913,19 +27917,19 @@
       </c>
       <c r="K402" s="60"/>
       <c r="L402" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M402" s="56">
+        <v>8</v>
+      </c>
+      <c r="N402" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M402" s="56">
-        <v>0</v>
-      </c>
-      <c r="N402" s="62">
+      <c r="O402" s="65">
         <f t="shared" si="21"/>
-        <v>8</v>
-      </c>
-      <c r="O402" s="65">
-        <f t="shared" si="22"/>
-        <v>88000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="403" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -27966,19 +27970,19 @@
       </c>
       <c r="K403" s="60"/>
       <c r="L403" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M403" s="56">
+        <v>4</v>
+      </c>
+      <c r="N403" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M403" s="56">
-        <v>0</v>
-      </c>
-      <c r="N403" s="62">
+      <c r="O403" s="65">
         <f t="shared" si="21"/>
-        <v>4</v>
-      </c>
-      <c r="O403" s="65">
-        <f t="shared" si="22"/>
-        <v>58000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="404" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28019,19 +28023,19 @@
       </c>
       <c r="K404" s="60"/>
       <c r="L404" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M404" s="56">
+        <v>5</v>
+      </c>
+      <c r="N404" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M404" s="56">
-        <v>0</v>
-      </c>
-      <c r="N404" s="62">
+      <c r="O404" s="65">
         <f t="shared" si="21"/>
-        <v>5</v>
-      </c>
-      <c r="O404" s="65">
-        <f t="shared" si="22"/>
-        <v>17500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="405" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28072,19 +28076,19 @@
       </c>
       <c r="K405" s="60"/>
       <c r="L405" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M405" s="56">
+        <v>8</v>
+      </c>
+      <c r="N405" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M405" s="56">
-        <v>0</v>
-      </c>
-      <c r="N405" s="62">
+      <c r="O405" s="65">
         <f t="shared" si="21"/>
-        <v>8</v>
-      </c>
-      <c r="O405" s="65">
-        <f t="shared" si="22"/>
-        <v>44000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="406" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28125,19 +28129,19 @@
       </c>
       <c r="K406" s="60"/>
       <c r="L406" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M406" s="56">
+        <v>2</v>
+      </c>
+      <c r="N406" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M406" s="56">
-        <v>0</v>
-      </c>
-      <c r="N406" s="62">
+      <c r="O406" s="65">
         <f t="shared" si="21"/>
-        <v>2</v>
-      </c>
-      <c r="O406" s="65">
-        <f t="shared" si="22"/>
-        <v>18000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="407" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28178,19 +28182,19 @@
       </c>
       <c r="K407" s="60"/>
       <c r="L407" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M407" s="56">
+        <v>4</v>
+      </c>
+      <c r="N407" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M407" s="56">
-        <v>0</v>
-      </c>
-      <c r="N407" s="62">
+      <c r="O407" s="65">
         <f t="shared" si="21"/>
-        <v>4</v>
-      </c>
-      <c r="O407" s="65">
-        <f t="shared" si="22"/>
-        <v>140000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28231,19 +28235,19 @@
       </c>
       <c r="K408" s="60"/>
       <c r="L408" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M408" s="56">
+        <v>6</v>
+      </c>
+      <c r="N408" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M408" s="56">
-        <v>0</v>
-      </c>
-      <c r="N408" s="62">
+      <c r="O408" s="65">
         <f t="shared" si="21"/>
-        <v>6</v>
-      </c>
-      <c r="O408" s="65">
-        <f t="shared" si="22"/>
-        <v>138000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="409" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28284,19 +28288,19 @@
       </c>
       <c r="K409" s="60"/>
       <c r="L409" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M409" s="56">
+        <v>1</v>
+      </c>
+      <c r="N409" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M409" s="56">
-        <v>0</v>
-      </c>
-      <c r="N409" s="62">
+      <c r="O409" s="65">
         <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="O409" s="65">
-        <f t="shared" si="22"/>
-        <v>21000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="410" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28337,19 +28341,19 @@
       </c>
       <c r="K410" s="60"/>
       <c r="L410" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M410" s="56">
+        <v>2</v>
+      </c>
+      <c r="N410" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M410" s="56">
-        <v>0</v>
-      </c>
-      <c r="N410" s="62">
+      <c r="O410" s="65">
         <f t="shared" si="21"/>
-        <v>2</v>
-      </c>
-      <c r="O410" s="65">
-        <f t="shared" si="22"/>
-        <v>72000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28390,19 +28394,19 @@
       </c>
       <c r="K411" s="60"/>
       <c r="L411" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M411" s="56">
+        <v>2</v>
+      </c>
+      <c r="N411" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M411" s="56">
-        <v>0</v>
-      </c>
-      <c r="N411" s="62">
+      <c r="O411" s="65">
         <f t="shared" si="21"/>
-        <v>2</v>
-      </c>
-      <c r="O411" s="65">
-        <f t="shared" si="22"/>
-        <v>46000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="412" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28443,19 +28447,19 @@
       </c>
       <c r="K412" s="60"/>
       <c r="L412" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M412" s="56">
+        <v>6</v>
+      </c>
+      <c r="N412" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M412" s="56">
-        <v>0</v>
-      </c>
-      <c r="N412" s="62">
+      <c r="O412" s="65">
         <f t="shared" si="21"/>
-        <v>6</v>
-      </c>
-      <c r="O412" s="65">
-        <f t="shared" si="22"/>
-        <v>90000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="413" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28496,19 +28500,19 @@
       </c>
       <c r="K413" s="60"/>
       <c r="L413" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M413" s="56">
+        <v>4</v>
+      </c>
+      <c r="N413" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M413" s="56">
-        <v>0</v>
-      </c>
-      <c r="N413" s="62">
+      <c r="O413" s="65">
         <f t="shared" si="21"/>
-        <v>4</v>
-      </c>
-      <c r="O413" s="65">
-        <f t="shared" si="22"/>
-        <v>72000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="414" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28549,19 +28553,19 @@
       </c>
       <c r="K414" s="60"/>
       <c r="L414" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M414" s="56">
+        <v>1</v>
+      </c>
+      <c r="N414" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M414" s="56">
-        <v>0</v>
-      </c>
-      <c r="N414" s="62">
+      <c r="O414" s="65">
         <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="O414" s="65">
-        <f t="shared" si="22"/>
-        <v>21000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="415" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28602,19 +28606,19 @@
       </c>
       <c r="K415" s="60"/>
       <c r="L415" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M415" s="56">
+        <v>2</v>
+      </c>
+      <c r="N415" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M415" s="56">
-        <v>0</v>
-      </c>
-      <c r="N415" s="62">
+      <c r="O415" s="65">
         <f t="shared" si="21"/>
-        <v>2</v>
-      </c>
-      <c r="O415" s="65">
-        <f t="shared" si="22"/>
-        <v>70000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="416" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28655,19 +28659,19 @@
       </c>
       <c r="K416" s="60"/>
       <c r="L416" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M416" s="56">
+        <v>4</v>
+      </c>
+      <c r="N416" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M416" s="56">
-        <v>0</v>
-      </c>
-      <c r="N416" s="62">
+      <c r="O416" s="65">
         <f t="shared" si="21"/>
-        <v>4</v>
-      </c>
-      <c r="O416" s="65">
-        <f t="shared" si="22"/>
-        <v>160000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="417" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28708,19 +28712,19 @@
       </c>
       <c r="K417" s="60"/>
       <c r="L417" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M417" s="56">
+        <v>1</v>
+      </c>
+      <c r="N417" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M417" s="56">
-        <v>0</v>
-      </c>
-      <c r="N417" s="62">
+      <c r="O417" s="65">
         <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="O417" s="65">
-        <f t="shared" si="22"/>
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="418" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28753,7 +28757,7 @@
         <v>0</v>
       </c>
       <c r="I418" s="56">
-        <f t="shared" ref="I418:I449" si="24">L355+M355+J418</f>
+        <f t="shared" ref="I418:I448" si="24">L355+M355+J418</f>
         <v>10</v>
       </c>
       <c r="J418" s="62">
@@ -28761,19 +28765,19 @@
       </c>
       <c r="K418" s="60"/>
       <c r="L418" s="13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M418" s="56">
+        <v>10</v>
+      </c>
+      <c r="N418" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M418" s="56">
-        <v>0</v>
-      </c>
-      <c r="N418" s="62">
-        <f t="shared" ref="N418:N448" si="25">MAX($I418-$M418,0)</f>
-        <v>10</v>
-      </c>
       <c r="O418" s="65">
-        <f t="shared" ref="O418:O449" si="26">N418*D418</f>
-        <v>20000</v>
+        <f t="shared" ref="O418:O448" si="25">N418*D418</f>
+        <v>0</v>
       </c>
     </row>
     <row r="419" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28814,19 +28818,19 @@
       </c>
       <c r="K419" s="60"/>
       <c r="L419" s="13">
-        <f t="shared" ref="L419:L448" si="27">IF(H419&gt;MAX(G419-M419,0),MAX(G419-M419,0),H419)</f>
+        <f t="shared" ref="L419:L448" si="26">IF(H419&gt;MAX(G419-M419,0),MAX(G419-M419,0),H419)</f>
         <v>0</v>
       </c>
       <c r="M419" s="56">
-        <v>0</v>
-      </c>
-      <c r="N419" s="62">
+        <v>10</v>
+      </c>
+      <c r="N419" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O419" s="65">
         <f t="shared" si="25"/>
-        <v>10</v>
-      </c>
-      <c r="O419" s="65">
-        <f t="shared" si="26"/>
-        <v>25000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28867,19 +28871,19 @@
       </c>
       <c r="K420" s="60"/>
       <c r="L420" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M420" s="56">
-        <v>0</v>
-      </c>
-      <c r="N420" s="62">
+        <v>11</v>
+      </c>
+      <c r="N420" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O420" s="65">
         <f t="shared" si="25"/>
-        <v>11</v>
-      </c>
-      <c r="O420" s="65">
-        <f t="shared" si="26"/>
-        <v>110000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="421" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28920,19 +28924,19 @@
       </c>
       <c r="K421" s="60"/>
       <c r="L421" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M421" s="56">
-        <v>0</v>
-      </c>
-      <c r="N421" s="62">
+        <v>10</v>
+      </c>
+      <c r="N421" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O421" s="65">
         <f t="shared" si="25"/>
-        <v>10</v>
-      </c>
-      <c r="O421" s="65">
-        <f t="shared" si="26"/>
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="422" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -28973,19 +28977,19 @@
       </c>
       <c r="K422" s="60"/>
       <c r="L422" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M422" s="56">
-        <v>0</v>
-      </c>
-      <c r="N422" s="62">
+        <v>6</v>
+      </c>
+      <c r="N422" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O422" s="65">
         <f t="shared" si="25"/>
-        <v>6</v>
-      </c>
-      <c r="O422" s="65">
-        <f t="shared" si="26"/>
-        <v>138000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="423" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -29026,19 +29030,19 @@
       </c>
       <c r="K423" s="60"/>
       <c r="L423" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M423" s="56">
-        <v>0</v>
-      </c>
-      <c r="N423" s="62">
+        <v>8</v>
+      </c>
+      <c r="N423" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O423" s="65">
         <f t="shared" si="25"/>
-        <v>8</v>
-      </c>
-      <c r="O423" s="65">
-        <f t="shared" si="26"/>
-        <v>88000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="424" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -29079,19 +29083,19 @@
       </c>
       <c r="K424" s="60"/>
       <c r="L424" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M424" s="56">
-        <v>0</v>
-      </c>
-      <c r="N424" s="62">
+        <v>4</v>
+      </c>
+      <c r="N424" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O424" s="65">
         <f t="shared" si="25"/>
-        <v>4</v>
-      </c>
-      <c r="O424" s="65">
-        <f t="shared" si="26"/>
-        <v>58000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="425" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -29132,19 +29136,19 @@
       </c>
       <c r="K425" s="60"/>
       <c r="L425" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M425" s="56">
-        <v>0</v>
-      </c>
-      <c r="N425" s="62">
+        <v>16</v>
+      </c>
+      <c r="N425" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O425" s="65">
         <f t="shared" si="25"/>
-        <v>16</v>
-      </c>
-      <c r="O425" s="65">
-        <f t="shared" si="26"/>
-        <v>56000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="426" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -29185,19 +29189,19 @@
       </c>
       <c r="K426" s="60"/>
       <c r="L426" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M426" s="56">
-        <v>0</v>
-      </c>
-      <c r="N426" s="62">
+        <v>8</v>
+      </c>
+      <c r="N426" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O426" s="65">
         <f t="shared" si="25"/>
-        <v>8</v>
-      </c>
-      <c r="O426" s="65">
-        <f t="shared" si="26"/>
-        <v>44000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="427" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -29238,19 +29242,19 @@
       </c>
       <c r="K427" s="60"/>
       <c r="L427" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M427" s="56">
-        <v>0</v>
-      </c>
-      <c r="N427" s="62">
+        <v>1</v>
+      </c>
+      <c r="N427" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O427" s="65">
         <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="O427" s="65">
-        <f t="shared" si="26"/>
-        <v>9000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="428" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -29291,19 +29295,19 @@
       </c>
       <c r="K428" s="60"/>
       <c r="L428" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M428" s="56">
-        <v>0</v>
-      </c>
-      <c r="N428" s="62">
+        <v>3</v>
+      </c>
+      <c r="N428" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O428" s="65">
         <f t="shared" si="25"/>
-        <v>3</v>
-      </c>
-      <c r="O428" s="65">
-        <f t="shared" si="26"/>
-        <v>105000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="429" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -29344,19 +29348,19 @@
       </c>
       <c r="K429" s="60"/>
       <c r="L429" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M429" s="56">
-        <v>0</v>
-      </c>
-      <c r="N429" s="62">
+        <v>6</v>
+      </c>
+      <c r="N429" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O429" s="65">
         <f t="shared" si="25"/>
-        <v>6</v>
-      </c>
-      <c r="O429" s="65">
-        <f t="shared" si="26"/>
-        <v>138000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="430" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -29397,18 +29401,18 @@
       </c>
       <c r="K430" s="60"/>
       <c r="L430" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M430" s="56">
         <v>0</v>
       </c>
-      <c r="N430" s="62">
+      <c r="N430" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O430" s="65">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="O430" s="65">
-        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -29450,18 +29454,18 @@
       </c>
       <c r="K431" s="60"/>
       <c r="L431" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M431" s="56">
         <v>0</v>
       </c>
-      <c r="N431" s="62">
+      <c r="N431" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O431" s="65">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="O431" s="65">
-        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -29503,19 +29507,19 @@
       </c>
       <c r="K432" s="60"/>
       <c r="L432" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M432" s="56">
-        <v>0</v>
-      </c>
-      <c r="N432" s="62">
+        <v>2</v>
+      </c>
+      <c r="N432" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O432" s="65">
         <f t="shared" si="25"/>
-        <v>2</v>
-      </c>
-      <c r="O432" s="65">
-        <f t="shared" si="26"/>
-        <v>46000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="433" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -29556,19 +29560,19 @@
       </c>
       <c r="K433" s="60"/>
       <c r="L433" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M433" s="56">
-        <v>0</v>
-      </c>
-      <c r="N433" s="62">
+        <v>6</v>
+      </c>
+      <c r="N433" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O433" s="65">
         <f t="shared" si="25"/>
-        <v>6</v>
-      </c>
-      <c r="O433" s="65">
-        <f t="shared" si="26"/>
-        <v>90000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="434" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -29609,18 +29613,18 @@
       </c>
       <c r="K434" s="60"/>
       <c r="L434" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M434" s="56">
         <v>0</v>
       </c>
-      <c r="N434" s="62">
+      <c r="N434" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O434" s="65">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="O434" s="65">
-        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -29662,19 +29666,19 @@
       </c>
       <c r="K435" s="60"/>
       <c r="L435" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M435" s="56">
-        <v>0</v>
-      </c>
-      <c r="N435" s="62">
+        <v>2</v>
+      </c>
+      <c r="N435" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O435" s="65">
         <f t="shared" si="25"/>
-        <v>2</v>
-      </c>
-      <c r="O435" s="65">
-        <f t="shared" si="26"/>
-        <v>42000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="436" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -29715,19 +29719,19 @@
       </c>
       <c r="K436" s="60"/>
       <c r="L436" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M436" s="56">
-        <v>0</v>
-      </c>
-      <c r="N436" s="62">
+        <v>2</v>
+      </c>
+      <c r="N436" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O436" s="65">
         <f t="shared" si="25"/>
-        <v>2</v>
-      </c>
-      <c r="O436" s="65">
-        <f t="shared" si="26"/>
-        <v>70000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="437" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -29768,19 +29772,19 @@
       </c>
       <c r="K437" s="60"/>
       <c r="L437" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M437" s="56">
-        <v>0</v>
-      </c>
-      <c r="N437" s="62">
+        <v>4</v>
+      </c>
+      <c r="N437" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O437" s="65">
         <f t="shared" si="25"/>
-        <v>4</v>
-      </c>
-      <c r="O437" s="65">
-        <f t="shared" si="26"/>
-        <v>160000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="438" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -29821,19 +29825,19 @@
       </c>
       <c r="K438" s="60"/>
       <c r="L438" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M438" s="56">
-        <v>0</v>
-      </c>
-      <c r="N438" s="62">
+        <v>1</v>
+      </c>
+      <c r="N438" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O438" s="65">
         <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="O438" s="65">
-        <f t="shared" si="26"/>
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="439" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -29874,19 +29878,19 @@
       </c>
       <c r="K439" s="60"/>
       <c r="L439" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M439" s="56">
-        <v>0</v>
-      </c>
-      <c r="N439" s="62">
+        <v>10</v>
+      </c>
+      <c r="N439" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O439" s="65">
         <f t="shared" si="25"/>
-        <v>10</v>
-      </c>
-      <c r="O439" s="65">
-        <f t="shared" si="26"/>
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -29927,19 +29931,19 @@
       </c>
       <c r="K440" s="60"/>
       <c r="L440" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M440" s="56">
-        <v>0</v>
-      </c>
-      <c r="N440" s="62">
+        <v>10</v>
+      </c>
+      <c r="N440" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O440" s="65">
         <f t="shared" si="25"/>
-        <v>10</v>
-      </c>
-      <c r="O440" s="65">
-        <f t="shared" si="26"/>
-        <v>25000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="441" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -29980,19 +29984,19 @@
       </c>
       <c r="K441" s="60"/>
       <c r="L441" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M441" s="56">
-        <v>0</v>
-      </c>
-      <c r="N441" s="62">
+        <v>15</v>
+      </c>
+      <c r="N441" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O441" s="65">
         <f t="shared" si="25"/>
-        <v>15</v>
-      </c>
-      <c r="O441" s="65">
-        <f t="shared" si="26"/>
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="442" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -30033,19 +30037,19 @@
       </c>
       <c r="K442" s="60"/>
       <c r="L442" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M442" s="56">
-        <v>0</v>
-      </c>
-      <c r="N442" s="62">
+        <v>6</v>
+      </c>
+      <c r="N442" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O442" s="65">
         <f t="shared" si="25"/>
-        <v>6</v>
-      </c>
-      <c r="O442" s="65">
-        <f t="shared" si="26"/>
-        <v>90000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="443" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -30086,19 +30090,19 @@
       </c>
       <c r="K443" s="60"/>
       <c r="L443" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M443" s="56">
-        <v>0</v>
-      </c>
-      <c r="N443" s="62">
+        <v>2</v>
+      </c>
+      <c r="N443" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O443" s="65">
         <f t="shared" si="25"/>
-        <v>2</v>
-      </c>
-      <c r="O443" s="65">
-        <f t="shared" si="26"/>
-        <v>46000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="444" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -30139,19 +30143,19 @@
       </c>
       <c r="K444" s="60"/>
       <c r="L444" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M444" s="56">
-        <v>0</v>
-      </c>
-      <c r="N444" s="62">
+        <v>8</v>
+      </c>
+      <c r="N444" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O444" s="65">
         <f t="shared" si="25"/>
-        <v>8</v>
-      </c>
-      <c r="O444" s="65">
-        <f t="shared" si="26"/>
-        <v>88000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="445" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -30192,19 +30196,19 @@
       </c>
       <c r="K445" s="60"/>
       <c r="L445" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M445" s="56">
-        <v>0</v>
-      </c>
-      <c r="N445" s="62">
+        <v>2</v>
+      </c>
+      <c r="N445" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O445" s="65">
         <f t="shared" si="25"/>
-        <v>2</v>
-      </c>
-      <c r="O445" s="65">
-        <f t="shared" si="26"/>
-        <v>29000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="446" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -30245,19 +30249,19 @@
       </c>
       <c r="K446" s="60"/>
       <c r="L446" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M446" s="56">
-        <v>0</v>
-      </c>
-      <c r="N446" s="62">
+        <v>15</v>
+      </c>
+      <c r="N446" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O446" s="65">
         <f t="shared" si="25"/>
-        <v>15</v>
-      </c>
-      <c r="O446" s="65">
-        <f t="shared" si="26"/>
-        <v>52500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="447" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -30298,19 +30302,19 @@
       </c>
       <c r="K447" s="60"/>
       <c r="L447" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M447" s="56">
-        <v>0</v>
-      </c>
-      <c r="N447" s="62">
+        <v>8</v>
+      </c>
+      <c r="N447" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O447" s="65">
         <f t="shared" si="25"/>
-        <v>8</v>
-      </c>
-      <c r="O447" s="65">
-        <f t="shared" si="26"/>
-        <v>44000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="448" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
@@ -30351,18 +30355,18 @@
       </c>
       <c r="K448" s="60"/>
       <c r="L448" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M448" s="56">
         <v>0</v>
       </c>
-      <c r="N448" s="62">
+      <c r="N448" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="O448" s="65">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="O448" s="65">
-        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
